--- a/public/fat-to-fit-sample-week.xlsx
+++ b/public/fat-to-fit-sample-week.xlsx
@@ -277,7 +277,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="P2" s="6">
@@ -299,7 +299,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="P3" s="6">
@@ -321,7 +321,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="P4" s="6">
@@ -343,51 +343,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C5" s="3">
-        <v>84</v>
-      </c>
-      <c r="D5" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="E5" s="3">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3">
-        <v>62</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Push</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>chest, shoulders, triceps</t>
-        </is>
-      </c>
-      <c r="J5" s="3">
-        <v>2150</v>
-      </c>
-      <c r="K5" s="3">
-        <v>148</v>
-      </c>
-      <c r="L5" s="3">
-        <v>215</v>
-      </c>
-      <c r="M5" s="3">
-        <v>62</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="P5" s="6">
@@ -409,20 +365,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C6" s="3">
-        <v>83.9</v>
+        <v>84</v>
       </c>
       <c r="D6" s="3">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="E6" s="3">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="F6" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -431,25 +387,25 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pull</t>
+          <t>Push</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>back, biceps, forearms</t>
+          <t>chest, shoulders, triceps</t>
         </is>
       </c>
       <c r="J6" s="3">
-        <v>2080</v>
+        <v>2150</v>
       </c>
       <c r="K6" s="3">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L6" s="3">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="M6" s="3">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -475,47 +431,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C7" s="3">
-        <v>83.6</v>
+        <v>83.9</v>
       </c>
       <c r="D7" s="3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="E7" s="3">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="F7" s="3">
+        <v>61</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>back, biceps, forearms</t>
+        </is>
+      </c>
+      <c r="J7" s="3">
+        <v>2080</v>
+      </c>
+      <c r="K7" s="3">
+        <v>152</v>
+      </c>
+      <c r="L7" s="3">
+        <v>200</v>
+      </c>
+      <c r="M7" s="3">
         <v>60</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Legs</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>quads, hamstrings, glutes, calves</t>
-        </is>
-      </c>
-      <c r="J7" s="3">
-        <v>2190</v>
-      </c>
-      <c r="K7" s="3">
-        <v>145</v>
-      </c>
-      <c r="L7" s="3">
-        <v>230</v>
-      </c>
-      <c r="M7" s="3">
-        <v>58</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -541,20 +497,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C8" s="3">
-        <v>83.5</v>
+        <v>83.6</v>
       </c>
       <c r="D8" s="3">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="3">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="F8" s="3">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -563,29 +519,29 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Push</t>
+          <t>Legs</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>chest, shoulders, triceps</t>
+          <t>quads, hamstrings, glutes, calves</t>
         </is>
       </c>
       <c r="J8" s="3">
-        <v>2320</v>
+        <v>2190</v>
       </c>
       <c r="K8" s="3">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L8" s="3">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="M8" s="3">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P8" s="6">
@@ -607,20 +563,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C9" s="3">
-        <v>83.3</v>
+        <v>83.5</v>
       </c>
       <c r="D9" s="3">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="E9" s="3">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="F9" s="3">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -629,29 +585,29 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pull</t>
+          <t>Push</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>back, biceps, abs</t>
+          <t>chest, shoulders, triceps</t>
         </is>
       </c>
       <c r="J9" s="3">
-        <v>2100</v>
+        <v>2320</v>
       </c>
       <c r="K9" s="3">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="L9" s="3">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="M9" s="3">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P9" s="6">
@@ -673,20 +629,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C10" s="3">
-        <v>83.1</v>
+        <v>83.3</v>
       </c>
       <c r="D10" s="3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="E10" s="3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="F10" s="3">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -695,25 +651,25 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Legs</t>
+          <t>Pull</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>quads, hamstrings, glutes, calves</t>
+          <t>back, biceps, abs</t>
         </is>
       </c>
       <c r="J10" s="3">
-        <v>2170</v>
+        <v>2100</v>
       </c>
       <c r="K10" s="3">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="L10" s="3">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="M10" s="3">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -739,36 +695,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C11" s="3">
+        <v>83.1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>7.4</v>
+      </c>
+      <c r="E11" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="F11" s="3">
+        <v>60</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C11" s="3">
-        <v>83.2</v>
-      </c>
-      <c r="D11" s="3">
-        <v>8.1</v>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Legs</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>quads, hamstrings, glutes, calves</t>
         </is>
       </c>
       <c r="J11" s="3">
-        <v>2050</v>
+        <v>2170</v>
       </c>
       <c r="K11" s="3">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="L11" s="3">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="M11" s="3">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -794,7 +761,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C12" s="3">
+        <v>83.2</v>
+      </c>
+      <c r="D12" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Rest</t>
+        </is>
+      </c>
+      <c r="J12" s="3">
+        <v>2050</v>
+      </c>
+      <c r="K12" s="3">
+        <v>145</v>
+      </c>
+      <c r="L12" s="3">
+        <v>210</v>
+      </c>
+      <c r="M12" s="3">
+        <v>55</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P12" s="6">
@@ -816,7 +816,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P13" s="6">
@@ -838,7 +838,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P14" s="6">
@@ -860,7 +860,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P15" s="6">
@@ -882,7 +882,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P16" s="6">
@@ -904,7 +904,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P17" s="6">
@@ -926,7 +926,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="P18" s="6">
@@ -948,7 +948,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="P19" s="6">
@@ -970,7 +970,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="P20" s="6">
@@ -992,7 +992,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="P21" s="6">
@@ -1014,7 +1014,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="P22" s="6">
@@ -1036,7 +1036,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="P23" s="6">
@@ -1058,7 +1058,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="P24" s="6">
@@ -1080,7 +1080,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="P25" s="6">
@@ -1102,7 +1102,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="P26" s="6">
@@ -1124,7 +1124,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="P27" s="6">
@@ -1146,7 +1146,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="P28" s="6">
@@ -1168,7 +1168,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="P29" s="6">
@@ -1190,7 +1190,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="P30" s="6">
@@ -1212,7 +1212,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="P31" s="6">
@@ -1234,7 +1234,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="P32" s="6">
@@ -1256,7 +1256,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="P33" s="6">
@@ -1278,7 +1278,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="P34" s="6">
@@ -1300,7 +1300,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="P35" s="6">
@@ -1322,7 +1322,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="P36" s="6">
@@ -1344,7 +1344,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="P37" s="6">
@@ -1366,7 +1366,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="P38" s="6">
@@ -1388,7 +1388,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="P39" s="6">
@@ -1410,7 +1410,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="P40" s="6">
@@ -1432,7 +1432,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="P41" s="6">
@@ -1454,7 +1454,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="P42" s="6">
@@ -1476,7 +1476,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="P43" s="6">
@@ -1498,7 +1498,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="P44" s="6">
@@ -1520,7 +1520,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="P45" s="6">
@@ -1542,7 +1542,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="P46" s="6">
@@ -1564,7 +1564,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="P47" s="6">
@@ -1586,7 +1586,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="P48" s="6">
@@ -1608,7 +1608,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="P49" s="6">
@@ -1630,7 +1630,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="P50" s="6">
@@ -1652,7 +1652,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="P51" s="6">
@@ -1674,7 +1674,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="P52" s="6">
@@ -1696,7 +1696,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="P53" s="6">
@@ -1718,7 +1718,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="P54" s="6">
@@ -1740,7 +1740,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="P55" s="6">
@@ -1762,7 +1762,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="P56" s="6">
@@ -1784,7 +1784,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="P57" s="6">
@@ -1806,7 +1806,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="P58" s="6">
@@ -1828,7 +1828,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="P59" s="6">
@@ -1850,7 +1850,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="P60" s="6">
@@ -1872,7 +1872,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="P61" s="6">
@@ -1894,7 +1894,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="P62" s="6">
@@ -1916,7 +1916,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="P63" s="6">
@@ -1938,7 +1938,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="P64" s="6">
@@ -1960,7 +1960,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="P65" s="6">
@@ -1982,7 +1982,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="P66" s="6">
@@ -2004,7 +2004,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="P67" s="6">
@@ -2026,7 +2026,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="P68" s="6">
@@ -2048,7 +2048,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="P69" s="6">
@@ -2070,7 +2070,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="P70" s="6">
@@ -2092,7 +2092,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="P71" s="6">
@@ -2114,7 +2114,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="P72" s="6">
@@ -2136,7 +2136,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="P73" s="6">
@@ -2158,7 +2158,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="P74" s="6">
@@ -2180,7 +2180,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="P75" s="6">
@@ -2202,7 +2202,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="P76" s="6">
@@ -2224,7 +2224,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="P77" s="6">
@@ -2246,7 +2246,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="P78" s="6">
@@ -2268,7 +2268,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="P79" s="6">
@@ -2290,7 +2290,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="P80" s="6">
@@ -2312,7 +2312,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>2027-01-02</t>
         </is>
       </c>
       <c r="P81" s="6">
@@ -2334,7 +2334,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="P82" s="6">
@@ -2356,7 +2356,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="P83" s="6">
@@ -2378,7 +2378,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="P84" s="6">
@@ -2400,7 +2400,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="P85" s="6">
@@ -2422,7 +2422,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="P86" s="6">
@@ -2444,7 +2444,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2027-01-08</t>
         </is>
       </c>
       <c r="P87" s="6">
@@ -2466,7 +2466,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2027-01-10</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="P88" s="6">
@@ -2488,7 +2488,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2027-01-11</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="P89" s="6">
@@ -2510,7 +2510,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2027-01-12</t>
+          <t>2027-01-11</t>
         </is>
       </c>
       <c r="P90" s="6">
@@ -2532,7 +2532,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="P91" s="6">
@@ -2554,7 +2554,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="P92" s="6">
@@ -2576,7 +2576,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="P93" s="6">
@@ -2598,7 +2598,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="P94" s="6">
@@ -2620,7 +2620,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="P95" s="6">
@@ -2642,7 +2642,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="P96" s="6">
@@ -2664,7 +2664,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="P97" s="6">
@@ -2686,7 +2686,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="P98" s="6">
@@ -2708,7 +2708,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="P99" s="6">
@@ -2730,7 +2730,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="P100" s="6">
@@ -2752,7 +2752,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="P101" s="6">
@@ -2774,7 +2774,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="P102" s="6">
@@ -2796,7 +2796,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="P103" s="6">
@@ -2818,7 +2818,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="P104" s="6">
@@ -2840,7 +2840,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="P105" s="6">
@@ -2862,7 +2862,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="P106" s="6">
@@ -2884,7 +2884,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="P107" s="6">
@@ -2906,7 +2906,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2027-01-30</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="P108" s="6">
@@ -2928,7 +2928,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-01-30</t>
         </is>
       </c>
       <c r="P109" s="6">
@@ -2950,7 +2950,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="P110" s="6">
@@ -2972,7 +2972,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2027-02-02</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="P111" s="6">
@@ -2994,7 +2994,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2027-02-02</t>
         </is>
       </c>
       <c r="P112" s="6">
@@ -3016,7 +3016,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-02-03</t>
         </is>
       </c>
       <c r="P113" s="6">
@@ -3038,7 +3038,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="P114" s="6">
@@ -3060,7 +3060,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2027-02-06</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="P115" s="6">
@@ -3082,7 +3082,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2027-02-07</t>
+          <t>2027-02-06</t>
         </is>
       </c>
       <c r="P116" s="6">
@@ -3104,7 +3104,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2027-02-08</t>
+          <t>2027-02-07</t>
         </is>
       </c>
       <c r="P117" s="6">
@@ -3126,7 +3126,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2027-02-09</t>
+          <t>2027-02-08</t>
         </is>
       </c>
       <c r="P118" s="6">
@@ -3148,7 +3148,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-02-09</t>
         </is>
       </c>
       <c r="P119" s="6">
@@ -3170,7 +3170,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2027-02-11</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="P120" s="6">
@@ -3192,7 +3192,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2027-02-12</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="P121" s="6">
